--- a/week-02/Ex4B_survey_results.xlsx
+++ b/week-02/Ex4B_survey_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/ilee_my_yearupunited_org/Documents/Documents/DataAnalytics/week-02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1216771-28C4-4372-A3F7-99E35A8AF7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{C1216771-28C4-4372-A3F7-99E35A8AF7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9EF21BC-F4E8-4931-9226-B741C4CBC801}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A1C1A52B-421E-42D1-8641-AE9D765AB187}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="13680" xr2:uid="{A1C1A52B-421E-42D1-8641-AE9D765AB187}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex4B_survey_results" sheetId="1" r:id="rId1"/>
@@ -41,48 +41,12 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Start time</t>
-  </si>
-  <si>
-    <t>Completion time</t>
-  </si>
-  <si>
     <t>Email</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>How would you rate the overall quality of your meal today?</t>
-  </si>
-  <si>
-    <t>Please indicate your overall satisfaction with Red Robins item selections.</t>
-  </si>
-  <si>
-    <t>Quick! Which is your go to Red Robin guilty pleasure?</t>
-  </si>
-  <si>
-    <t>How likely are you to recommend us to the friends and family?</t>
-  </si>
-  <si>
-    <t>There can only be one.</t>
-  </si>
-  <si>
-    <t>Are you a Red Robin Rewards Member?</t>
-  </si>
-  <si>
-    <t>How likely are you to return back to this Red Robin location?</t>
-  </si>
-  <si>
-    <t>How satisfied are you with the manner of time in which you received your order?</t>
-  </si>
-  <si>
-    <t>How well would you rate your service and experience with Red Robins Today?</t>
-  </si>
-  <si>
-    <t>Do you have any feedback, comments, or suggestions you would like to provide?</t>
-  </si>
-  <si>
     <t>ilee@my.yearupunited.org</t>
   </si>
   <si>
@@ -162,13 +126,49 @@
   </si>
   <si>
     <t>My overall experience was pleasant, keep up the great work!</t>
+  </si>
+  <si>
+    <t>start_time</t>
+  </si>
+  <si>
+    <t>completion_time</t>
+  </si>
+  <si>
+    <t>Quality_of_meal</t>
+  </si>
+  <si>
+    <t>Item_Selection_Satisfaction</t>
+  </si>
+  <si>
+    <t>Preferred_Appetizer</t>
+  </si>
+  <si>
+    <t>Overall_Recommend</t>
+  </si>
+  <si>
+    <t>Milkshake_v_Dirty_Soda</t>
+  </si>
+  <si>
+    <t>Rewards_Membership</t>
+  </si>
+  <si>
+    <t>Rate_of_Return_To_Location</t>
+  </si>
+  <si>
+    <t>Rate_of_Timiliness</t>
+  </si>
+  <si>
+    <t>Rate_of_Service_and_Experience</t>
+  </si>
+  <si>
+    <t>Feedback</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1024,56 +1024,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654456EF-2807-427F-9124-F852445963DC}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="72.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="154.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1084,28 +1099,28 @@
         <v>46309.969444444447</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -1117,10 +1132,10 @@
         <v>5</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1131,28 +1146,28 @@
         <v>46310.380555555559</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="L3">
         <v>10</v>
@@ -1164,10 +1179,10 @@
         <v>5</v>
       </c>
       <c r="O3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1178,28 +1193,28 @@
         <v>46311.564583333333</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -1211,10 +1226,10 @@
         <v>5</v>
       </c>
       <c r="O4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1225,28 +1240,28 @@
         <v>46311.696527777778</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I5">
         <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -1258,10 +1273,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1272,28 +1287,28 @@
         <v>46311.776388888888</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>8</v>
       </c>
       <c r="J6" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1305,10 +1320,10 @@
         <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1319,28 +1334,28 @@
         <v>46315.868055555555</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I7">
         <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1352,7 +1367,7 @@
         <v>5</v>
       </c>
       <c r="O7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
